--- a/excel_interno.xlsx
+++ b/excel_interno.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASEGURADOS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z175"/>
+  <dimension ref="A1:Z180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -11804,11 +11804,7 @@
       <c r="Z174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>31 de agosto dar de baja brandan</t>
-        </is>
-      </c>
+      <c r="A175" t="inlineStr"/>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
@@ -11835,6 +11831,174 @@
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
+      <c r="W177" t="inlineStr"/>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+      <c r="W178" t="inlineStr"/>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ramiro alejandro herrera</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1141492756</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>brava nevada 125</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>a189zhp</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>cuponera</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+      <c r="W179" t="inlineStr"/>
+      <c r="X179" t="inlineStr"/>
+      <c r="Y179" t="inlineStr"/>
+      <c r="Z179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_interno.xlsx
+++ b/excel_interno.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z180"/>
+  <dimension ref="A1:Z186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -11918,30 +11918,14 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ramiro alejandro herrera</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>1141492756</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>brava nevada 125</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>a189zhp</t>
-        </is>
-      </c>
+          <t>ramiro alejandroherrera</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>atm</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>cuponera</t>
@@ -11972,11 +11956,7 @@
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>si</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
@@ -11999,6 +11979,322 @@
       <c r="Y180" t="inlineStr"/>
       <c r="Z180" t="inlineStr"/>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>ramiro herrera</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1141492756</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>brava nevada 125</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>a189zhp</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>cuponera</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>passegurosyriesgos@gmail.com</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr"/>
+      <c r="Y181" t="inlineStr"/>
+      <c r="Z181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>ramiro herrera</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1141492756</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>brava nevada 125</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>a189zhp</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>cuponera</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>pas.segurosyriesgos@gmail.com</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr"/>
+      <c r="Z182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>pepito</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>676767</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>latercera</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>1764</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+      <c r="W183" t="inlineStr"/>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr"/>
+      <c r="Z183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TRANSPORTE ALEJO SRL</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>58813260</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>FLOTA COMPLETA (34 UNIDADES)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>La Segunda</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TRANSPORTE ALEJO SRL</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>58813260</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>FIAT STRADA 1.3 FIRE FLY FREEDOM CS 2025</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>AH638CX</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>La Segunda</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr"/>
+      <c r="Z185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>ramiro herrera</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1141492756</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>brava nevada 125</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>a189zhp</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>atm</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>cuponera</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_interno.xlsx
+++ b/excel_interno.xlsx
@@ -503,18 +503,11 @@
           <t>MAIL</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
-      <c r="Q1" t="inlineStr"/>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
-      <c r="W1" t="inlineStr"/>
-      <c r="X1" t="inlineStr"/>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>TELEFONO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -557,30 +550,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>60000.0</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>lautarostreet5@gmail.com</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -623,30 +602,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>10000.0</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>jraserabra@gmail.com</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -689,30 +654,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>25000.0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>raserhector2@gmail.com</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -755,30 +706,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>10000.0</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>raserhector2@gmail.com</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -821,30 +758,16 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>90000.0</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>julian.raser1@gmail.com</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -887,30 +810,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>15000.0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>jraserabra@gmail.com</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -953,30 +862,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>50000.0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>julian.raser1@gmail.com</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1019,30 +914,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>75000.0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>julian.raser1@gmail.com</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1085,30 +966,16 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>115000.0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>eduardofaure88@gmail.com</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1151,7 +1018,6 @@
           <t>1882.0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>100000.0</t>
@@ -1167,18 +1033,6 @@
           <t>cap-00@hotmail.com</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1221,30 +1075,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>40000.0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>penalvasilvia19@gmail.com</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1287,30 +1127,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>50000.0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>julian.raser1@gmail.com</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1353,30 +1179,16 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>115000.0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>julian.raser1@gmail.com</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1419,30 +1231,16 @@
           <t>1824.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>38000.0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>gustivillalba2@gmail.com</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1485,30 +1283,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>91000.0</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>facundo.logozzo@gmail.com</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1551,30 +1335,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>59000.0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>juli.adduca.ja@gmail.com</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1617,30 +1387,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>24500.0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>jraserabra@gmail.com</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1683,30 +1439,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>9000.0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>jraserabra@gmail.com</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1749,30 +1491,16 @@
           <t>1854.0</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>9000.0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>convertipaola@gmail.com</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1815,30 +1543,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>44000.0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>raserhector2@gmail.com</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1881,30 +1595,16 @@
           <t>1864.0</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>9000.0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>julian.raser1@gmail.com</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1947,30 +1647,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>45000.0</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>Nahuellogozzo90@gmail.com</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2013,30 +1699,16 @@
           <t>7607.0</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>10000.0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>lautarostreet5@gmail.com</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2079,26 +1751,11 @@
           <t>1864.0</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>7900.0</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2141,30 +1798,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>10000.0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>julian.raser1@gmail.com</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2207,30 +1850,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>40000.0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>cami_9211@hotmail.com</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2273,30 +1902,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>50000.0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>jraserabra@gmail.com</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2339,30 +1954,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>177000.0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>facundo.logozzo@gmail.com</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2405,30 +2006,16 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>51000.0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>jraserabra@gmail.com</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2471,30 +2058,16 @@
           <t>1864.0</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>42000.0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>GABRIELHECTORESPONISA@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2537,30 +2110,16 @@
           <t>1640.0</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>32000.0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>benjateoquintans@gmail.com</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2603,26 +2162,11 @@
           <t>1876.0</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>32000.0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2665,30 +2209,16 @@
           <t>1417.0</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>66000.0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>martindamianbao@gmail.com</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2731,30 +2261,16 @@
           <t>1417.0</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>70000.0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>martindamianbao@gmail.com</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2797,26 +2313,11 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>10000.0</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2859,30 +2360,16 @@
           <t>1414.0</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>72000.0</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>baogaston01@gmail.com</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2925,26 +2412,11 @@
           <t>1856.0</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>51000.0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2987,30 +2459,16 @@
           <t>1417.0</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>82000.0</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>martindamianbao@gmail.com</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3053,30 +2511,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>44000.0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>facundo.logozzo@gmail.com</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3119,30 +2563,16 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>50000.0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>marinaarodriguezz08@gmail.com</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
-      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3185,30 +2615,16 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>113000.0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>MARIANASOLEDADAYALA94@GMAIL.COM</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3251,7 +2667,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>36000.0</t>
@@ -3262,19 +2677,6 @@
           <t>auto guille</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3317,7 +2719,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>18000.0</t>
@@ -3333,18 +2734,6 @@
           <t>davidgutierrez53@gmail.com</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3387,7 +2776,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>36000.0</t>
@@ -3398,19 +2786,6 @@
           <t xml:space="preserve">cayo oficina </t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3453,7 +2828,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>65000.0</t>
@@ -3464,19 +2838,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3519,7 +2880,6 @@
           <t>1636.0</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>185000.0</t>
@@ -3535,18 +2895,6 @@
           <t xml:space="preserve"> titoantartico@gmail.com</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3589,7 +2937,6 @@
           <t>1636.0</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>103000.0</t>
@@ -3605,18 +2952,6 @@
           <t>Mauro.lescano84@gmail.com</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3659,7 +2994,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>69000.0</t>
@@ -3670,19 +3004,6 @@
           <t xml:space="preserve">cayo oficina </t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3725,7 +3046,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>19500.0</t>
@@ -3736,19 +3056,6 @@
           <t xml:space="preserve">cayo oficina </t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3791,7 +3098,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>65000.0</t>
@@ -3802,19 +3108,6 @@
           <t>contacto juli</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3857,7 +3150,6 @@
           <t>1834.0</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>44000.0</t>
@@ -3868,19 +3160,6 @@
           <t xml:space="preserve">cayo oficina </t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3923,7 +3202,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>132000.0</t>
@@ -3939,18 +3217,6 @@
           <t>diegokasjan@hotmail.com</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3993,7 +3259,6 @@
           <t>1864.0</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>30000.0</t>
@@ -4004,19 +3269,6 @@
           <t xml:space="preserve">conocido ramon </t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4059,7 +3311,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>47000.0</t>
@@ -4070,19 +3321,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4125,7 +3363,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>88000.0</t>
@@ -4136,19 +3373,6 @@
           <t>cayo oficina</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4191,7 +3415,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>55000.0</t>
@@ -4202,19 +3425,6 @@
           <t xml:space="preserve">conocido ramon </t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4257,7 +3467,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>88000.0</t>
@@ -4268,19 +3477,6 @@
           <t>contacto fer</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4323,7 +3519,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>140000.0</t>
@@ -4334,19 +3529,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4389,7 +3571,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>31500.0</t>
@@ -4400,19 +3581,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4455,7 +3623,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>56000.0</t>
@@ -4466,19 +3633,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4521,7 +3675,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -4532,19 +3685,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4587,7 +3727,6 @@
           <t>1881.0</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>41000.0</t>
@@ -4598,19 +3737,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4653,7 +3779,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>67000.0</t>
@@ -4664,19 +3789,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4719,7 +3831,6 @@
           <t>1864.0</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>13000.0</t>
@@ -4730,19 +3841,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
-      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4785,7 +3883,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -4796,19 +3893,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4851,7 +3935,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>113000.0</t>
@@ -4862,19 +3945,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4917,7 +3987,6 @@
           <t>1870.0</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>33000.0</t>
@@ -4928,19 +3997,6 @@
           <t>ramon</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4983,7 +4039,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>21200.0</t>
@@ -4994,19 +4049,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5049,7 +4091,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>4757.0</t>
@@ -5060,19 +4101,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5115,7 +4143,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>1816.0</t>
@@ -5126,19 +4153,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5181,7 +4195,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>12646.0</t>
@@ -5192,19 +4205,6 @@
           <t>fer</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5247,7 +4247,6 @@
           <t>1856.0</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>95000.0</t>
@@ -5258,19 +4257,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5313,7 +4299,6 @@
           <t>1417.0</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>86000.0</t>
@@ -5324,19 +4309,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5379,7 +4351,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>30000.0</t>
@@ -5390,19 +4361,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5445,7 +4403,6 @@
           <t>1417.0</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>67000.0</t>
@@ -5456,19 +4413,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5511,7 +4455,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>11500.0</t>
@@ -5522,19 +4465,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5577,7 +4507,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>75000.0</t>
@@ -5588,19 +4517,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5643,7 +4559,6 @@
           <t>1834.0</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>96000.0</t>
@@ -5659,18 +4574,6 @@
           <t>ROBO TOTAL</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5714,7 +4617,6 @@
           <t>1033.0</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>73000.0</t>
@@ -5725,19 +4627,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5780,7 +4669,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>183000.0</t>
@@ -5791,19 +4679,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5846,7 +4721,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>214000.0</t>
@@ -5857,19 +4731,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5912,7 +4773,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>237000.0</t>
@@ -5923,19 +4783,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5978,7 +4825,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>85000.0</t>
@@ -5989,19 +4835,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6044,7 +4877,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>84000.0</t>
@@ -6055,19 +4887,6 @@
           <t>contacto guille</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6110,26 +4929,11 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>90367.0</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6172,7 +4976,6 @@
           <t>1856.0</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -6183,19 +4986,6 @@
           <t>fernanda</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6238,26 +5028,11 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>12591.0</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6301,7 +5076,6 @@
           <t>1824.0</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -6312,19 +5086,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6368,7 +5129,6 @@
           <t>1881.0</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -6379,19 +5139,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6434,7 +5181,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>86500.0</t>
@@ -6445,19 +5191,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6500,7 +5233,6 @@
           <t>1888.0</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -6511,19 +5243,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6566,7 +5285,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -6577,19 +5295,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6633,7 +5338,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -6644,19 +5348,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6699,7 +5390,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -6710,19 +5400,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6766,7 +5443,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -6777,19 +5453,6 @@
           <t>fernanda</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6832,7 +5495,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -6843,19 +5505,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6898,7 +5547,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>23500.0</t>
@@ -6909,19 +5557,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6964,7 +5599,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>42000.0</t>
@@ -6975,19 +5609,6 @@
           <t>guille</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7031,7 +5652,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -7042,19 +5662,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7097,7 +5704,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>76500.0</t>
@@ -7108,19 +5714,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7163,7 +5756,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>40000.0</t>
@@ -7174,19 +5766,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7224,7 +5803,6 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Introduce un valor adecuado para esta celda según el contexto de la tabla"")"),"1846")</f>
         <v/>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -7235,19 +5813,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7290,7 +5855,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -7301,19 +5865,6 @@
           <t>rodri</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7356,7 +5907,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>71000.0</t>
@@ -7367,19 +5917,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7422,7 +5959,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -7433,19 +5969,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7488,7 +6011,6 @@
           <t>1416.0</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr">
         <is>
           <t>75000.0</t>
@@ -7499,19 +6021,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7554,7 +6063,6 @@
           <t>1854.0</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>102000.0</t>
@@ -7565,19 +6073,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7621,7 +6116,6 @@
           <t>1824.0</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>85000.0</t>
@@ -7632,19 +6126,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
-      <c r="W109" t="inlineStr"/>
-      <c r="X109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7687,7 +6168,6 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -7698,19 +6178,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
-      <c r="U110" t="inlineStr"/>
-      <c r="V110" t="inlineStr"/>
-      <c r="W110" t="inlineStr"/>
-      <c r="X110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7752,7 +6219,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -7763,19 +6229,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
-      <c r="U111" t="inlineStr"/>
-      <c r="V111" t="inlineStr"/>
-      <c r="W111" t="inlineStr"/>
-      <c r="X111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7818,7 +6271,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>58000.0</t>
@@ -7829,19 +6281,6 @@
           <t>guille</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
-      <c r="U112" t="inlineStr"/>
-      <c r="V112" t="inlineStr"/>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7884,7 +6323,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>4721.0</t>
@@ -7895,19 +6333,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
-      <c r="U113" t="inlineStr"/>
-      <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr"/>
-      <c r="X113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7950,7 +6375,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>2385.0</t>
@@ -7961,19 +6385,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
-      <c r="U114" t="inlineStr"/>
-      <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr"/>
-      <c r="X114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8016,7 +6427,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>2385.0</t>
@@ -8027,19 +6437,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
-      <c r="W115" t="inlineStr"/>
-      <c r="X115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8081,7 +6478,6 @@
           <t>1417.0</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>83840.0</t>
@@ -8092,19 +6488,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr"/>
-      <c r="W116" t="inlineStr"/>
-      <c r="X116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8147,7 +6530,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>89615.0</t>
@@ -8158,19 +6540,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
-      <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr"/>
-      <c r="X117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8213,7 +6582,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>56000.0</t>
@@ -8224,19 +6592,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
-      <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8272,7 +6627,6 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("AI(""Introduce un valor adecuado para esta celda según el contexto de la tabla"")"),"1865")</f>
         <v/>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>40000.0</t>
@@ -8283,19 +6637,6 @@
           <t>juli</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr"/>
-      <c r="V119" t="inlineStr"/>
-      <c r="W119" t="inlineStr"/>
-      <c r="X119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8338,7 +6679,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr">
         <is>
           <t>130000.0</t>
@@ -8349,19 +6689,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
-      <c r="U120" t="inlineStr"/>
-      <c r="V120" t="inlineStr"/>
-      <c r="W120" t="inlineStr"/>
-      <c r="X120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8404,7 +6731,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>63000.0</t>
@@ -8415,19 +6741,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
-      <c r="U121" t="inlineStr"/>
-      <c r="V121" t="inlineStr"/>
-      <c r="W121" t="inlineStr"/>
-      <c r="X121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8470,7 +6783,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>40000.0</t>
@@ -8481,19 +6793,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr"/>
-      <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
-      <c r="X122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8536,7 +6835,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr">
         <is>
           <t>109000.0</t>
@@ -8547,19 +6845,6 @@
           <t>fernanda</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
-      <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
-      <c r="V123" t="inlineStr"/>
-      <c r="W123" t="inlineStr"/>
-      <c r="X123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8602,7 +6887,6 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>83000.0</t>
@@ -8613,19 +6897,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
-      <c r="U124" t="inlineStr"/>
-      <c r="V124" t="inlineStr"/>
-      <c r="W124" t="inlineStr"/>
-      <c r="X124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8668,7 +6939,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr">
         <is>
           <t>78000.0</t>
@@ -8679,19 +6949,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
-      <c r="U125" t="inlineStr"/>
-      <c r="V125" t="inlineStr"/>
-      <c r="W125" t="inlineStr"/>
-      <c r="X125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8734,7 +6991,6 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -8745,19 +7001,6 @@
           <t>fernanda</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr"/>
-      <c r="V126" t="inlineStr"/>
-      <c r="W126" t="inlineStr"/>
-      <c r="X126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8800,7 +7043,6 @@
           <t>1285.0</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr">
         <is>
           <t>72000.0</t>
@@ -8811,19 +7053,6 @@
           <t>rodri</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr"/>
-      <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr"/>
-      <c r="X127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8866,7 +7095,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr">
         <is>
           <t>18500.0</t>
@@ -8877,19 +7105,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
-      <c r="U128" t="inlineStr"/>
-      <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8932,7 +7147,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>32000.0</t>
@@ -8943,19 +7157,6 @@
           <t>guillermo</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
-      <c r="U129" t="inlineStr"/>
-      <c r="V129" t="inlineStr"/>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8999,7 +7200,6 @@
           <t>1888.0</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -9010,19 +7210,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
-      <c r="U130" t="inlineStr"/>
-      <c r="V130" t="inlineStr"/>
-      <c r="W130" t="inlineStr"/>
-      <c r="X130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9065,7 +7252,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr">
         <is>
           <t>42000.0</t>
@@ -9076,19 +7262,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
-      <c r="U131" t="inlineStr"/>
-      <c r="V131" t="inlineStr"/>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9127,7 +7300,6 @@
           <t>1870.0</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -9138,19 +7310,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
-      <c r="U132" t="inlineStr"/>
-      <c r="V132" t="inlineStr"/>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9193,7 +7352,6 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>32000.0</t>
@@ -9204,19 +7362,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
-      <c r="U133" t="inlineStr"/>
-      <c r="V133" t="inlineStr"/>
-      <c r="W133" t="inlineStr"/>
-      <c r="X133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9259,7 +7404,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>18000.0</t>
@@ -9270,19 +7414,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
-      <c r="U134" t="inlineStr"/>
-      <c r="V134" t="inlineStr"/>
-      <c r="W134" t="inlineStr"/>
-      <c r="X134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9325,7 +7456,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>90000.0</t>
@@ -9336,19 +7466,6 @@
           <t>guillermo</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr"/>
-      <c r="U135" t="inlineStr"/>
-      <c r="V135" t="inlineStr"/>
-      <c r="W135" t="inlineStr"/>
-      <c r="X135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9391,7 +7508,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -9402,19 +7518,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
-      <c r="U136" t="inlineStr"/>
-      <c r="V136" t="inlineStr"/>
-      <c r="W136" t="inlineStr"/>
-      <c r="X136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9457,7 +7560,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -9468,19 +7570,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
-      <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
-      <c r="W137" t="inlineStr"/>
-      <c r="X137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9523,7 +7612,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>70000.0</t>
@@ -9534,19 +7622,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr"/>
-      <c r="V138" t="inlineStr"/>
-      <c r="W138" t="inlineStr"/>
-      <c r="X138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9589,7 +7664,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -9600,19 +7674,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr"/>
-      <c r="U139" t="inlineStr"/>
-      <c r="V139" t="inlineStr"/>
-      <c r="W139" t="inlineStr"/>
-      <c r="X139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9655,7 +7716,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>50000.0</t>
@@ -9666,19 +7726,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr"/>
-      <c r="U140" t="inlineStr"/>
-      <c r="V140" t="inlineStr"/>
-      <c r="W140" t="inlineStr"/>
-      <c r="X140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9721,7 +7768,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -9732,19 +7778,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
-      <c r="U141" t="inlineStr"/>
-      <c r="V141" t="inlineStr"/>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9787,7 +7820,6 @@
           <t>1856.0</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>61000.0</t>
@@ -9798,19 +7830,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr"/>
-      <c r="U142" t="inlineStr"/>
-      <c r="V142" t="inlineStr"/>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9853,7 +7872,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -9864,19 +7882,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr"/>
-      <c r="U143" t="inlineStr"/>
-      <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr"/>
-      <c r="X143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9919,7 +7924,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -9930,19 +7934,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
-      <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr"/>
-      <c r="W144" t="inlineStr"/>
-      <c r="X144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9985,7 +7976,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -9996,19 +7986,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr"/>
-      <c r="U145" t="inlineStr"/>
-      <c r="V145" t="inlineStr"/>
-      <c r="W145" t="inlineStr"/>
-      <c r="X145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10051,7 +8028,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -10062,19 +8038,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr"/>
-      <c r="U146" t="inlineStr"/>
-      <c r="V146" t="inlineStr"/>
-      <c r="W146" t="inlineStr"/>
-      <c r="X146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10117,7 +8080,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -10128,19 +8090,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
-      <c r="U147" t="inlineStr"/>
-      <c r="V147" t="inlineStr"/>
-      <c r="W147" t="inlineStr"/>
-      <c r="X147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10183,7 +8132,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>44000.0</t>
@@ -10194,19 +8142,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr"/>
-      <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
-      <c r="X148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10249,7 +8184,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -10260,19 +8194,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr"/>
-      <c r="U149" t="inlineStr"/>
-      <c r="V149" t="inlineStr"/>
-      <c r="W149" t="inlineStr"/>
-      <c r="X149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10315,7 +8236,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>56000.0</t>
@@ -10326,19 +8246,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
-      <c r="U150" t="inlineStr"/>
-      <c r="V150" t="inlineStr"/>
-      <c r="W150" t="inlineStr"/>
-      <c r="X150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10381,7 +8288,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>79000.0</t>
@@ -10392,19 +8298,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
-      <c r="U151" t="inlineStr"/>
-      <c r="V151" t="inlineStr"/>
-      <c r="W151" t="inlineStr"/>
-      <c r="X151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10447,7 +8340,6 @@
           <t>1881.0</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -10458,19 +8350,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
-      <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr"/>
-      <c r="W152" t="inlineStr"/>
-      <c r="X152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10513,7 +8392,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>174000.0</t>
@@ -10524,19 +8402,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
-      <c r="U153" t="inlineStr"/>
-      <c r="V153" t="inlineStr"/>
-      <c r="W153" t="inlineStr"/>
-      <c r="X153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10579,7 +8444,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>58000.0</t>
@@ -10590,19 +8454,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr"/>
-      <c r="W154" t="inlineStr"/>
-      <c r="X154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10645,7 +8496,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>50000.0</t>
@@ -10656,19 +8506,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr"/>
-      <c r="V155" t="inlineStr"/>
-      <c r="W155" t="inlineStr"/>
-      <c r="X155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10711,7 +8548,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -10722,19 +8558,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
-      <c r="W156" t="inlineStr"/>
-      <c r="X156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10777,7 +8600,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -10788,19 +8610,6 @@
           <t>fernanda</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
-      <c r="U157" t="inlineStr"/>
-      <c r="V157" t="inlineStr"/>
-      <c r="W157" t="inlineStr"/>
-      <c r="X157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10843,7 +8652,6 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -10854,19 +8662,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr"/>
-      <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
-      <c r="W158" t="inlineStr"/>
-      <c r="X158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10909,7 +8704,6 @@
           <t>1847.0</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -10920,19 +8714,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
-      <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
-      <c r="W159" t="inlineStr"/>
-      <c r="X159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10975,7 +8756,6 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>92500.0</t>
@@ -10986,19 +8766,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr"/>
-      <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
-      <c r="W160" t="inlineStr"/>
-      <c r="X160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11042,7 +8809,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -11053,19 +8819,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr"/>
-      <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
-      <c r="W161" t="inlineStr"/>
-      <c r="X161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11108,7 +8861,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -11119,19 +8871,6 @@
           <t>ramon</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr"/>
-      <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
-      <c r="W162" t="inlineStr"/>
-      <c r="X162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11174,7 +8913,6 @@
           <t>7105.0</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
           <t>39000.0</t>
@@ -11185,19 +8923,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
-      <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
-      <c r="W163" t="inlineStr"/>
-      <c r="X163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11205,7 +8930,6 @@
           <t>MALDONADO CARLOS ALBERTO</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>VW POLO COMFORTLINE</t>
@@ -11236,7 +8960,6 @@
           <t>1870.0</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
           <t>29000.0</t>
@@ -11247,19 +8970,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr"/>
-      <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
-      <c r="W164" t="inlineStr"/>
-      <c r="X164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11302,7 +9012,6 @@
           <t>1846.0</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>94000.0</t>
@@ -11313,19 +9022,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr"/>
-      <c r="U165" t="inlineStr"/>
-      <c r="V165" t="inlineStr"/>
-      <c r="W165" t="inlineStr"/>
-      <c r="X165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11343,7 +9039,6 @@
           <t xml:space="preserve">CORVEN MIRAGE RT </t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
           <t>NO</t>
@@ -11364,7 +9059,6 @@
           <t>1865.0</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>18000.0</t>
@@ -11375,19 +9069,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
-      <c r="T166" t="inlineStr"/>
-      <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr"/>
-      <c r="W166" t="inlineStr"/>
-      <c r="X166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11430,7 +9111,6 @@
           <t>1832.0</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
           <t>15000.0</t>
@@ -11441,19 +9121,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
-      <c r="T167" t="inlineStr"/>
-      <c r="U167" t="inlineStr"/>
-      <c r="V167" t="inlineStr"/>
-      <c r="W167" t="inlineStr"/>
-      <c r="X167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11511,19 +9178,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
-      <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr"/>
-      <c r="W168" t="inlineStr"/>
-      <c r="X168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11581,19 +9235,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
-      <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
-      <c r="W169" t="inlineStr"/>
-      <c r="X169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11651,19 +9292,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr"/>
-      <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
-      <c r="W170" t="inlineStr"/>
-      <c r="X170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11722,19 +9350,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr"/>
-      <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr"/>
-      <c r="W171" t="inlineStr"/>
-      <c r="X171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11792,19 +9407,6 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr"/>
-      <c r="U172" t="inlineStr"/>
-      <c r="V172" t="inlineStr"/>
-      <c r="W172" t="inlineStr"/>
-      <c r="X172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11862,361 +9464,25 @@
           <t>ofi</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr"/>
-      <c r="S173" t="inlineStr"/>
-      <c r="T173" t="inlineStr"/>
-      <c r="U173" t="inlineStr"/>
-      <c r="V173" t="inlineStr"/>
-      <c r="W173" t="inlineStr"/>
-      <c r="X173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr"/>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="inlineStr"/>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr"/>
-      <c r="U174" t="inlineStr"/>
-      <c r="V174" t="inlineStr"/>
-      <c r="W174" t="inlineStr"/>
-      <c r="X174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr"/>
-      <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr"/>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr"/>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr"/>
-      <c r="U175" t="inlineStr"/>
-      <c r="V175" t="inlineStr"/>
-      <c r="W175" t="inlineStr"/>
-      <c r="X175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr"/>
-      <c r="B176" t="inlineStr"/>
-      <c r="C176" t="inlineStr"/>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
-      <c r="S176" t="inlineStr"/>
-      <c r="T176" t="inlineStr"/>
-      <c r="U176" t="inlineStr"/>
-      <c r="V176" t="inlineStr"/>
-      <c r="W176" t="inlineStr"/>
-      <c r="X176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr"/>
-      <c r="B177" t="inlineStr"/>
-      <c r="C177" t="inlineStr"/>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
-      <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr"/>
-      <c r="V177" t="inlineStr"/>
-      <c r="W177" t="inlineStr"/>
-      <c r="X177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr"/>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
-      <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr"/>
-      <c r="U178" t="inlineStr"/>
-      <c r="V178" t="inlineStr"/>
-      <c r="W178" t="inlineStr"/>
-      <c r="X178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr"/>
-      <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
-      <c r="S179" t="inlineStr"/>
-      <c r="T179" t="inlineStr"/>
-      <c r="U179" t="inlineStr"/>
-      <c r="V179" t="inlineStr"/>
-      <c r="W179" t="inlineStr"/>
-      <c r="X179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr"/>
-      <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
-      <c r="U180" t="inlineStr"/>
-      <c r="V180" t="inlineStr"/>
-      <c r="W180" t="inlineStr"/>
-      <c r="X180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr"/>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
-      <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr"/>
-      <c r="U181" t="inlineStr"/>
-      <c r="V181" t="inlineStr"/>
-      <c r="W181" t="inlineStr"/>
-      <c r="X181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr"/>
-      <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
-      <c r="S182" t="inlineStr"/>
-      <c r="T182" t="inlineStr"/>
-      <c r="U182" t="inlineStr"/>
-      <c r="V182" t="inlineStr"/>
-      <c r="W182" t="inlineStr"/>
-      <c r="X182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr"/>
-      <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr"/>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
-      <c r="U183" t="inlineStr"/>
-      <c r="V183" t="inlineStr"/>
-      <c r="W183" t="inlineStr"/>
-      <c r="X183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr"/>
-      <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr"/>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
-      <c r="U184" t="inlineStr"/>
-      <c r="V184" t="inlineStr"/>
-      <c r="W184" t="inlineStr"/>
-      <c r="X184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
-      <c r="U185" t="inlineStr"/>
-      <c r="V185" t="inlineStr"/>
-      <c r="W185" t="inlineStr"/>
-      <c r="X185" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
           <t>31 de agosto dar de baja brandan</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr"/>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
-      <c r="U186" t="inlineStr"/>
-      <c r="V186" t="inlineStr"/>
-      <c r="W186" t="inlineStr"/>
-      <c r="X186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
